--- a/datasets/day1_excel_foundations/08_pivottables_and_what_if_analysis/d1_m8_pivottables_start.xlsx
+++ b/datasets/day1_excel_foundations/08_pivottables_and_what_if_analysis/d1_m8_pivottables_start.xlsx
@@ -462,7 +462,7 @@
     <col width="22.5" customWidth="1" min="7" max="7"/>
     <col width="12.5" customWidth="1" min="8" max="8"/>
     <col width="10.5" customWidth="1" min="9" max="9"/>
-    <col width="9.5" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -602,7 +602,7 @@
         <v>1</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>119.7</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4">
@@ -646,7 +646,7 @@
         <v>2</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>3332</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="5">
@@ -690,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1454.4</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="6">
@@ -734,7 +734,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>806</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7">
@@ -778,7 +778,7 @@
         <v>2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1656</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="8">
@@ -822,7 +822,7 @@
         <v>3</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>326.25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -866,7 +866,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>779.2</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
@@ -910,7 +910,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>587.2</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11">
@@ -954,7 +954,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>801.6</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="12">
@@ -998,7 +998,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1663</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="13">
@@ -1042,7 +1042,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1037</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14">
@@ -1086,7 +1086,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>724</v>
+        <v>800</v>
       </c>
     </row>
     <row r="15">
@@ -1130,7 +1130,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>177</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -1174,7 +1174,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>653.8</v>
+        <v>800</v>
       </c>
     </row>
     <row r="17">
@@ -1218,7 +1218,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1758</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="18">
@@ -1262,7 +1262,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>56.1</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19">
@@ -1306,7 +1306,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1148</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="20">
@@ -1350,7 +1350,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>905.25</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="21">
@@ -1394,7 +1394,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>918</v>
+        <v>600</v>
       </c>
     </row>
     <row r="22">
@@ -1438,7 +1438,7 @@
         <v>3</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1806.9</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="23">
@@ -1482,7 +1482,7 @@
         <v>1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>672.8</v>
+        <v>700</v>
       </c>
     </row>
     <row r="24">
@@ -1526,7 +1526,7 @@
         <v>2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>619.4</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25">
@@ -1570,7 +1570,7 @@
         <v>2</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>370</v>
+        <v>300</v>
       </c>
     </row>
     <row r="26">
@@ -1614,7 +1614,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>882</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="27">
@@ -1658,7 +1658,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>190.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -1702,7 +1702,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1696</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="29">
@@ -1746,7 +1746,7 @@
         <v>1</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>102.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -1790,7 +1790,7 @@
         <v>2</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>258.4</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31">
@@ -1834,7 +1834,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>263</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32">
@@ -1878,7 +1878,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>159</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33">
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>352</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34">
@@ -1966,7 +1966,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>148</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35">
@@ -2010,7 +2010,7 @@
         <v>2</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>226</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36">
@@ -2054,7 +2054,7 @@
         <v>1</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>289.85</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37">
@@ -2098,7 +2098,7 @@
         <v>1</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38">
@@ -2142,7 +2142,7 @@
         <v>4</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>4416</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="39">
@@ -2186,7 +2186,7 @@
         <v>2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>1160</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="40">
@@ -2230,7 +2230,7 @@
         <v>1</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>889.1</v>
+        <v>700</v>
       </c>
     </row>
     <row r="41">
@@ -2274,7 +2274,7 @@
         <v>1</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>115.9</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42">
@@ -2318,7 +2318,7 @@
         <v>1</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>303.05</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43">
@@ -2362,7 +2362,7 @@
         <v>1</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>710</v>
+        <v>800</v>
       </c>
     </row>
     <row r="44">
@@ -2406,7 +2406,7 @@
         <v>1</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>1245</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="45">
@@ -2450,7 +2450,7 @@
         <v>1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1009.6</v>
+        <v>800</v>
       </c>
     </row>
     <row r="46">
@@ -2494,7 +2494,7 @@
         <v>1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>782</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="47">
@@ -2538,7 +2538,7 @@
         <v>1</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>174</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48">
@@ -2582,7 +2582,7 @@
         <v>3</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>396</v>
+        <v>240</v>
       </c>
     </row>
     <row r="49">
@@ -2626,7 +2626,7 @@
         <v>1</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>1799</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="50">
@@ -2670,7 +2670,7 @@
         <v>1</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>1259</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="51">
@@ -2714,7 +2714,7 @@
         <v>1</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>146</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52">
@@ -2758,7 +2758,7 @@
         <v>4</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>3980</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="53">
@@ -2802,7 +2802,7 @@
         <v>1</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>1003</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="54">
@@ -2846,7 +2846,7 @@
         <v>1</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>794</v>
+        <v>900</v>
       </c>
     </row>
     <row r="55">
@@ -2890,7 +2890,7 @@
         <v>4</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>6777.6</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="56">
@@ -2934,7 +2934,7 @@
         <v>3</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>2898</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="57">
@@ -2978,7 +2978,7 @@
         <v>2</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>214</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58">
@@ -3022,7 +3022,7 @@
         <v>1</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>165.3</v>
+        <v>120</v>
       </c>
     </row>
     <row r="59">
@@ -3066,7 +3066,7 @@
         <v>1</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60">
@@ -3110,7 +3110,7 @@
         <v>2</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>2759.4</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="61">
@@ -3154,7 +3154,7 @@
         <v>3</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>1050</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="62">
@@ -3198,7 +3198,7 @@
         <v>1</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="63">
@@ -3242,7 +3242,7 @@
         <v>1</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>1928</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="64">
@@ -3286,7 +3286,7 @@
         <v>1</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>765</v>
+        <v>700</v>
       </c>
     </row>
     <row r="65">
@@ -3330,7 +3330,7 @@
         <v>2</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>212</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66">
@@ -3374,7 +3374,7 @@
         <v>1</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>1581</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="67">
@@ -3418,7 +3418,7 @@
         <v>1</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>1433</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="68">
@@ -3462,7 +3462,7 @@
         <v>1</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>1737</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="69">
@@ -3506,7 +3506,7 @@
         <v>1</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>812</v>
+        <v>700</v>
       </c>
     </row>
     <row r="70">
@@ -3550,7 +3550,7 @@
         <v>1</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>1244</v>
+        <v>900</v>
       </c>
     </row>
     <row r="71">
@@ -3594,7 +3594,7 @@
         <v>1</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>312</v>
+        <v>150</v>
       </c>
     </row>
     <row r="72">
@@ -3638,7 +3638,7 @@
         <v>2</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>2561.4</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="73">
@@ -3682,7 +3682,7 @@
         <v>1</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>645</v>
+        <v>500</v>
       </c>
     </row>
     <row r="74">
@@ -3726,7 +3726,7 @@
         <v>1</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>548.25</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="75">
@@ -3770,7 +3770,7 @@
         <v>1</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>43.2</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76">
@@ -3814,7 +3814,7 @@
         <v>1</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="77">
@@ -3858,7 +3858,7 @@
         <v>1</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>1996</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="78">
@@ -3902,7 +3902,7 @@
         <v>1</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>1608.35</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="79">
@@ -3946,7 +3946,7 @@
         <v>1</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>848</v>
+        <v>800</v>
       </c>
     </row>
     <row r="80">
@@ -3990,7 +3990,7 @@
         <v>1</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>94.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81">
@@ -4034,7 +4034,7 @@
         <v>1</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>135</v>
+        <v>60</v>
       </c>
     </row>
     <row r="82">
@@ -4078,7 +4078,7 @@
         <v>4</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>2052</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="83">
@@ -4122,7 +4122,7 @@
         <v>1</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>1138</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="84">
@@ -4166,7 +4166,7 @@
         <v>2</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>1310</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="85">
@@ -4210,7 +4210,7 @@
         <v>1</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>949</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="86">
@@ -4254,7 +4254,7 @@
         <v>2</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>812</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="87">
@@ -4298,7 +4298,7 @@
         <v>2</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>154</v>
+        <v>240</v>
       </c>
     </row>
     <row r="88">
@@ -4342,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89">
@@ -4386,7 +4386,7 @@
         <v>1</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>126</v>
+        <v>100</v>
       </c>
     </row>
     <row r="90">
@@ -4430,7 +4430,7 @@
         <v>1</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>105</v>
+        <v>200</v>
       </c>
     </row>
     <row r="91">
@@ -4474,7 +4474,7 @@
         <v>1</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>856</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="92">
@@ -4518,7 +4518,7 @@
         <v>3</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>1638.9</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="93">
@@ -4562,7 +4562,7 @@
         <v>2</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>254</v>
+        <v>160</v>
       </c>
     </row>
     <row r="94">
@@ -4606,7 +4606,7 @@
         <v>4</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>2385.6</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="95">
@@ -4650,7 +4650,7 @@
         <v>1</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>693.7</v>
+        <v>500</v>
       </c>
     </row>
     <row r="96">
@@ -4694,7 +4694,7 @@
         <v>2</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>3236</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="97">
@@ -4738,7 +4738,7 @@
         <v>3</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>2706</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="98">
@@ -4782,7 +4782,7 @@
         <v>1</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>1538</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="99">
@@ -4826,7 +4826,7 @@
         <v>1</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>114.75</v>
+        <v>150</v>
       </c>
     </row>
     <row r="100">
@@ -4870,7 +4870,7 @@
         <v>2</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>56</v>
+        <v>240</v>
       </c>
     </row>
     <row r="101">
@@ -4914,7 +4914,7 @@
         <v>1</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>33.6</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -5138,7 +5138,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">            To value:      18000</t>
+          <t xml:space="preserve">            To value:      16000</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Click OK. Excel finds the exact price increase needed (about 12.6%).</t>
+          <t xml:space="preserve">          Click OK. Excel finds the exact price increase needed (about 10%).</t>
         </is>
       </c>
     </row>

--- a/datasets/day1_excel_foundations/08_pivottables_and_what_if_analysis/d1_m8_pivottables_start.xlsx
+++ b/datasets/day1_excel_foundations/08_pivottables_and_what_if_analysis/d1_m8_pivottables_start.xlsx
@@ -1427,7 +1427,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>100 orders. Far too many to read. A PivotTable summarises them in about ten seconds.</t>
+          <t>20 orders - but even 20 rows is slow to total by hand, category by category. A PivotTable does it in seconds (and real data has thousands).</t>
         </is>
       </c>
     </row>

--- a/datasets/day1_excel_foundations/08_pivottables_and_what_if_analysis/d1_m8_pivottables_start.xlsx
+++ b/datasets/day1_excel_foundations/08_pivottables_and_what_if_analysis/d1_m8_pivottables_start.xlsx
@@ -1408,7 +1408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A44"/>
+  <dimension ref="A1:A46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1569,134 +1569,136 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>PART C - WHAT-IF ANALYSIS</t>
+          <t>PART C - WHAT-IF ANALYSIS (Goal Seek)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Go to the 'What-If' sheet. The model is already built. Play with it.</t>
+          <t>Go to the 'What-If' sheet. Everything here is on that one sheet - no other sheet.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>STEP 11 - Change the 'Price Increase' cell (B5) from 0% to 10%.</t>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   B4 = Laptops to sell     B5 = Price each (1000)     B7 = Total sales  (=B4*B5)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          Watch Projected Revenue and Projected Profit update.</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>STEP 12 - Now work backwards with Goal Seek.</t>
+          <t>STEP 11 - The normal way (forwards): change B4 (laptops) and watch B7 (total sales)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Data tab &gt; What-If Analysis &gt; Goal Seek.</t>
+          <t xml:space="preserve">          update. You change an input, the formula gives the answer.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Set cell:      B13   (Projected Profit)</t>
-        </is>
-      </c>
+      <c r="A31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            To value:      3000</t>
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>STEP 12 - Goal Seek (backwards): we want Total sales to be exactly 10000.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">            By changing:   B5    (Price Increase)</t>
+          <t xml:space="preserve">          Data tab &gt; What-If Analysis &gt; Goal Seek.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Click OK. Excel finds the exact price increase needed (about 7%).</t>
+          <t xml:space="preserve">            Set cell:      B7      (Total sales - the cell with the formula)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">          This is the single most useful What-If tool in Excel - it answers</t>
+          <t xml:space="preserve">            To value:      10000</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">          'what would we have to do to get there?'</t>
+          <t xml:space="preserve">            By changing:   B4      (Laptops to sell - a plain number)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>STEP 13 - Data tab &gt; What-If Analysis &gt; Scenario Manager. Add two scenarios that</t>
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          Click OK. Excel works backwards and puts 10 in B4  (10 x 1000 = 10000).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">          change B5: 'Cautious' at 3% and 'Aggressive' at 12%. Then click Summary</t>
+          <t xml:space="preserve">          That is Goal Seek: you know the answer you want, Excel finds the input.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          to get a side-by-side comparison report.</t>
-        </is>
-      </c>
+      <c r="A39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr"/>
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>STEP 13 - Scenario Manager (optional). Data &gt; What-If Analysis &gt; Scenario Manager.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>CHECK YOURSELF: the answers workbook has a 'Pivot Result' sheet showing the numbers</t>
+          <t xml:space="preserve">          Add two scenarios that change B4: 'Modest' at 8 and 'Ambitious' at 15.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>your PivotTable should produce (built with SUMIFS so you can see the logic underneath),</t>
+          <t xml:space="preserve">          Click Summary for a side-by-side comparison of the Total sales each gives.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>and a fully working What-If sheet.</t>
-        </is>
-      </c>
+      <c r="A43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n"/>
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>CHECK YOURSELF: the answers workbook has a 'Pivot Result' sheet showing the numbers</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>your PivotTable should produce, and the finished What-If sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datasets/day1_excel_foundations/08_pivottables_and_what_if_analysis/d1_m8_pivottables_start.xlsx
+++ b/datasets/day1_excel_foundations/08_pivottables_and_what_if_analysis/d1_m8_pivottables_start.xlsx
@@ -1408,7 +1408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A46"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1662,43 +1662,88 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>STEP 13 - Scenario Manager (optional). Data &gt; What-If Analysis &gt; Scenario Manager.</t>
+          <t>STEP 13 - Now on REAL DATA (lower down, same sheet). B12 is our real sales total -</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Add two scenarios that change B4: 'Modest' at 8 and 'Ambitious' at 15.</t>
+          <t xml:space="preserve">          it adds the Sales column from the Orders sheet. B13 is a growth %, and</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Click Summary for a side-by-side comparison of the Total sales each gives.</t>
+          <t xml:space="preserve">          B14 is the projected total (=B12*(1+B13)). We want B14 to reach 20000.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr"/>
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          Goal Seek: Set cell B14, To value 20000, By changing B13.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>CHECK YOURSELF: the answers workbook has a 'Pivot Result' sheet showing the numbers</t>
+          <t xml:space="preserve">          Excel finds about 13.4% - a number you could NOT do in your head. THAT is</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">          where Goal Seek earns its keep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>STEP 14 - Scenario Manager (optional). Data &gt; What-If Analysis &gt; Scenario Manager.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          Add two scenarios that change B4: 'Modest' at 8 and 'Ambitious' at 15.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          Click Summary for a side-by-side comparison of the Total sales each gives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>CHECK YOURSELF: the answers workbook has a 'Pivot Result' sheet showing the numbers</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
           <t>your PivotTable should produce, and the finished What-If sheet.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="n"/>
+    <row r="53">
+      <c r="A53" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
